--- a/data/processed/harmonization/Acidity__Soil_pH/10.15485_1868940/10.15485_1868940_soil_Acidity__Soil_pH.xlsx
+++ b/data/processed/harmonization/Acidity__Soil_pH/10.15485_1868940/10.15485_1868940_soil_Acidity__Soil_pH.xlsx
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>TOOL:1:3:14-35</t>
+          <t>TOOL:3:14-35:1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -575,12 +575,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>TOOL:2:1:30-40</t>
+          <t>TOOL:1:30-40:2</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -626,12 +626,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>HEAL:3:1:12-24</t>
+          <t>HEAL:1:12-24:3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>HEAL:5:1:0-12</t>
+          <t>HEAL:1:0-12:5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -728,12 +728,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>HEAL:6:3:16-30</t>
+          <t>HEAL:3:16-30:6</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -779,12 +779,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>HEAL:7:3:16-30</t>
+          <t>HEAL:3:16-30:7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>TOOL:8:2:20-28</t>
+          <t>TOOL:2:20-28:8</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>HEAL:9:2:20-28</t>
+          <t>HEAL:2:20-28:9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>TOOL:10:1:20-30</t>
+          <t>TOOL:1:20-30:10</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -983,12 +983,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>HEAL:11:3:0-9</t>
+          <t>HEAL:3:0-9:11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>TOOL:12:3:14-35</t>
+          <t>TOOL:3:14-35:12</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>TOOL:13:1:10-20</t>
+          <t>TOOL:1:10-20:13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>TOOL:14:2:10-20</t>
+          <t>TOOL:2:10-20:14</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>HEAL:15:1:12-24</t>
+          <t>HEAL:1:12-24:15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>HEAL:16:2:12-20</t>
+          <t>HEAL:2:12-20:16</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>HEAL:1:1:50-60</t>
+          <t>HEAL:1:50-60:1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>HEAL:2:1:50-60</t>
+          <t>HEAL:1:50-60:2</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1391,12 +1391,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>HEAL:3:2:34-47</t>
+          <t>HEAL:2:34-47:3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>HEAL:4:2:28-34</t>
+          <t>HEAL:2:28-34:4</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>HEAL:5:1:50-60</t>
+          <t>HEAL:1:50-60:5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>TOOL:6:1:60-67</t>
+          <t>TOOL:1:60-67:6</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>HEAL:7:3:40-54</t>
+          <t>HEAL:3:40-54:7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>HEAL:8:3:40-54</t>
+          <t>HEAL:3:40-54:8</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>HEAL:9:1:24-33</t>
+          <t>HEAL:1:24-33:9</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>TOOL:10:3:35-41</t>
+          <t>TOOL:3:35-41:10</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>TOOL:11:2:38-44</t>
+          <t>TOOL:2:38-44:11</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>HEAL:12:2:47-68</t>
+          <t>HEAL:2:47-68:12</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>HEAL:13:3:30-38</t>
+          <t>HEAL:3:30-38:13</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>TOOL:14:3:41-50</t>
+          <t>TOOL:3:41-50:14</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>TOOL:15:1:50-60</t>
+          <t>TOOL:1:50-60:15</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>TOOL:16:2:44-58</t>
+          <t>TOOL:2:44-58:16</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>TOOL:17:3:50-58</t>
+          <t>TOOL:3:50-58:17</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>TOOL:18:1:40-50</t>
+          <t>TOOL:1:40-50:18</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>TOOL:19:2:28-38</t>
+          <t>TOOL:2:28-38:19</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>HEAL:20:1:33-50</t>
+          <t>HEAL:1:33-50:20</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Site:Lab ID:Rep:depth</t>
+          <t>Site:Rep:depth:Lab ID</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
